--- a/03_Charts/VAE/FinancialRatios/XGBoost/StrategyA/Error_Summary.xlsx
+++ b/03_Charts/VAE/FinancialRatios/XGBoost/StrategyA/Error_Summary.xlsx
@@ -20,16 +20,16 @@
     <t xml:space="preserve">Count</t>
   </si>
   <si>
+    <t xml:space="preserve">Median_Net Debt Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median_Self-Financing Ratio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Median_Return on Assets (ROA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Median_Net Debt Ratio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Median_Return on Fixed Assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median_Self-Financing Ratio</t>
   </si>
   <si>
     <t xml:space="preserve">Median_Cash to Current Assets</t>
@@ -401,22 +401,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>138507</v>
+        <v>124851</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04031465093412</v>
+        <v>-0.270546165605293</v>
       </c>
       <c r="D2" t="n">
-        <v>0.516445470282747</v>
+        <v>0.260828933781494</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0892759934676102</v>
+        <v>0.206122150062574</v>
       </c>
       <c r="F2" t="n">
-        <v>0.188228080931944</v>
+        <v>0.1609556593004</v>
       </c>
       <c r="G2" t="n">
-        <v>0.185031185031185</v>
+        <v>0.219331072448149</v>
       </c>
     </row>
     <row r="3">
@@ -424,22 +424,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>21523</v>
+        <v>35179</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.062575210589651</v>
+        <v>0.917769486345602</v>
       </c>
       <c r="D3" t="n">
-        <v>1.04471544715447</v>
+        <v>-1.00064269988814</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.17816091954023</v>
+        <v>-0.946424730191164</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.203617571059432</v>
+        <v>-0.970306213217676</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0132275132275132</v>
+        <v>-0.664153371167991</v>
       </c>
     </row>
     <row r="4">
@@ -447,22 +447,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0246415103178507</v>
+        <v>0.0723030399419715</v>
       </c>
       <c r="D4" t="n">
-        <v>0.724134762770111</v>
+        <v>-0.0138766742638323</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0509756218132512</v>
+        <v>-0.0523272749485278</v>
       </c>
       <c r="F4" t="n">
-        <v>0.115619737558777</v>
+        <v>-0.066718290007709</v>
       </c>
       <c r="G4" t="n">
-        <v>0.110806596234065</v>
+        <v>-0.0258877774004207</v>
       </c>
     </row>
     <row r="5">
@@ -470,22 +470,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1220</v>
+        <v>1164</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0553445357703882</v>
+        <v>1.05275688794948</v>
       </c>
       <c r="D5" t="n">
-        <v>0.990577618606327</v>
+        <v>-1.16725513046169</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.13543362481462</v>
+        <v>-1.18076672473183</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.175286259541985</v>
+        <v>-1.18458749705223</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0176419381068542</v>
+        <v>-0.639511653263057</v>
       </c>
     </row>
   </sheetData>
